--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486830_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486830_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.4062</v>
+        <v>4.762</v>
       </c>
       <c r="E2" t="n">
-        <v>2.9079</v>
+        <v>2.8597</v>
       </c>
       <c r="F2" t="n">
-        <v>2.4983</v>
+        <v>1.9023</v>
       </c>
       <c r="G2" t="n">
         <v>3.8901</v>
@@ -610,13 +610,13 @@
         <v>1.3515</v>
       </c>
       <c r="S2" t="n">
-        <v>1.8097</v>
+        <v>1.1655</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6339</v>
+        <v>0.5857</v>
       </c>
       <c r="U2" t="n">
-        <v>1.1758</v>
+        <v>0.5798</v>
       </c>
       <c r="V2" t="n">
         <v>0.2856</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.4255</v>
+        <v>4.2557</v>
       </c>
       <c r="E3" t="n">
-        <v>1.7148</v>
+        <v>2.4457</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7107</v>
+        <v>1.81</v>
       </c>
       <c r="G3" t="n">
         <v>3.1137</v>
@@ -688,13 +688,13 @@
         <v>0.9654</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.9818</v>
+        <v>-0.1515</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8829</v>
+        <v>-0.152</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0989</v>
+        <v>0.0005</v>
       </c>
       <c r="V3" t="n">
         <v>0.3282</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.3725</v>
+        <v>4.1724</v>
       </c>
       <c r="E4" t="n">
-        <v>1.9733</v>
+        <v>2.649</v>
       </c>
       <c r="F4" t="n">
-        <v>1.3992</v>
+        <v>1.5234</v>
       </c>
       <c r="G4" t="n">
         <v>3.7586</v>
@@ -766,13 +766,13 @@
         <v>0.9654</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3861</v>
+        <v>0.4138</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5243</v>
+        <v>0.1514</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1382</v>
+        <v>0.2624</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. FORTES SILVA</t>
+          <t>A. GUERRERO PAEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.2321</v>
+        <v>2.9698</v>
       </c>
       <c r="E5" t="n">
-        <v>2.5395</v>
+        <v>1.0187</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6927</v>
+        <v>1.9511</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8254</v>
+        <v>2.0663</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.2823</v>
+        <v>0.5652</v>
       </c>
       <c r="I5" t="n">
-        <v>1.1076</v>
+        <v>1.5011</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5162</v>
+        <v>1.1499</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.4197</v>
+        <v>0.0828</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9359</v>
+        <v>1.0671</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3092</v>
+        <v>0.9164</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1374</v>
+        <v>0.4824</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1717</v>
+        <v>0.434</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.5446</v>
+        <v>0.9654</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.8962</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3515</v>
+        <v>0.9654</v>
       </c>
       <c r="S5" t="n">
-        <v>2.4381</v>
+        <v>-0.0619</v>
       </c>
       <c r="T5" t="n">
-        <v>2.1784</v>
+        <v>-0.1312</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2597</v>
+        <v>0.0693</v>
       </c>
       <c r="V5" t="n">
-        <v>1.5133</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>2.741</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2277</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. GUERRERO PAEZ</t>
+          <t>A. FORTES SILVA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.734</v>
+        <v>2.1456</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7085</v>
+        <v>1.3536</v>
       </c>
       <c r="F6" t="n">
-        <v>2.0255</v>
+        <v>0.792</v>
       </c>
       <c r="G6" t="n">
-        <v>2.0663</v>
+        <v>0.8254</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5652</v>
+        <v>-0.2823</v>
       </c>
       <c r="I6" t="n">
-        <v>1.5011</v>
+        <v>1.1076</v>
       </c>
       <c r="J6" t="n">
-        <v>1.1499</v>
+        <v>0.5162</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0828</v>
+        <v>-0.4197</v>
       </c>
       <c r="L6" t="n">
-        <v>1.0671</v>
+        <v>0.9359</v>
       </c>
       <c r="M6" t="n">
-        <v>0.9164</v>
+        <v>0.3092</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4824</v>
+        <v>0.1374</v>
       </c>
       <c r="O6" t="n">
-        <v>0.434</v>
+        <v>0.1717</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9654</v>
+        <v>-1.5446</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.8962</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9654</v>
+        <v>1.3515</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2977</v>
+        <v>1.3515</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4415</v>
+        <v>0.9926</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1438</v>
+        <v>0.359</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.5133</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.741</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. SANTOLARIA MARTIN</t>
+          <t>R. TERRATS MADRID</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9014</v>
+        <v>0.637</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8883</v>
+        <v>-0.2933</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0131</v>
+        <v>0.9303</v>
       </c>
       <c r="G7" t="n">
-        <v>0.033</v>
+        <v>2.8452</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.3377</v>
+        <v>2.124</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3707</v>
+        <v>0.7211</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0888</v>
+        <v>1.4597</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0074</v>
+        <v>1.9865</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0814</v>
+        <v>-0.5266999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.0558</v>
+        <v>1.3854</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3451</v>
+        <v>0.1376</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2893</v>
+        <v>1.2478</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1931</v>
+        <v>-0.1931</v>
       </c>
       <c r="Q7" t="n">
         <v>-0.9654</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1585</v>
+        <v>0.7723</v>
       </c>
       <c r="S7" t="n">
-        <v>1.903</v>
+        <v>-0.1309</v>
       </c>
       <c r="T7" t="n">
-        <v>1.7649</v>
+        <v>-0.1312</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1381</v>
+        <v>0.0003</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.2277</v>
+        <v>-1.8842</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>-0.6565</v>
       </c>
       <c r="X7" t="n">
         <v>-1.2277</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8574000000000001</v>
+        <v>0.2506</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3537</v>
+        <v>-0.0048</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5038</v>
+        <v>0.2554</v>
       </c>
       <c r="G8" t="n">
         <v>1.2121</v>
@@ -1078,13 +1078,13 @@
         <v>1.1585</v>
       </c>
       <c r="S8" t="n">
-        <v>0.9655</v>
+        <v>0.3587</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6616</v>
+        <v>0.3031</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3039</v>
+        <v>0.0556</v>
       </c>
       <c r="V8" t="n">
         <v>-1.5133</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. TERRATS MADRID</t>
+          <t>J. SANTOLARIA MARTIN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2771</v>
+        <v>0.1292</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.6036</v>
+        <v>0.1161</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8807</v>
+        <v>0.0131</v>
       </c>
       <c r="G9" t="n">
-        <v>2.8452</v>
+        <v>0.033</v>
       </c>
       <c r="H9" t="n">
-        <v>2.124</v>
+        <v>-0.3377</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7211</v>
+        <v>0.3707</v>
       </c>
       <c r="J9" t="n">
-        <v>1.4597</v>
+        <v>0.0888</v>
       </c>
       <c r="K9" t="n">
-        <v>1.9865</v>
+        <v>0.0074</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5266999999999999</v>
+        <v>0.0814</v>
       </c>
       <c r="M9" t="n">
-        <v>1.3854</v>
+        <v>-0.0558</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1376</v>
+        <v>-0.3451</v>
       </c>
       <c r="O9" t="n">
-        <v>1.2478</v>
+        <v>0.2893</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.1931</v>
+        <v>0.1931</v>
       </c>
       <c r="Q9" t="n">
         <v>-0.9654</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7723</v>
+        <v>1.1585</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4908</v>
+        <v>1.1308</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4415</v>
+        <v>0.9927</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0494</v>
+        <v>0.1381</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.8842</v>
+        <v>-1.2277</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.6565</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>-1.2277</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.998</v>
+        <v>-0.8972</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.2203</v>
+        <v>-3.2685</v>
       </c>
       <c r="F10" t="n">
-        <v>2.2223</v>
+        <v>2.3713</v>
       </c>
       <c r="G10" t="n">
         <v>-2.078</v>
@@ -1234,13 +1234,13 @@
         <v>1.1585</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2924</v>
+        <v>0.3932</v>
       </c>
       <c r="T10" t="n">
-        <v>0.5512</v>
+        <v>0.503</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2588</v>
+        <v>-0.1098</v>
       </c>
       <c r="V10" t="n">
         <v>-0.3709</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.6664</v>
+        <v>-1.007</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.668</v>
+        <v>-2.406</v>
       </c>
       <c r="F11" t="n">
-        <v>1.0016</v>
+        <v>1.399</v>
       </c>
       <c r="G11" t="n">
         <v>-1.6579</v>
@@ -1312,13 +1312,13 @@
         <v>1.5446</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2594</v>
+        <v>0.3999</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0279</v>
+        <v>0.2341</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2315</v>
+        <v>0.1658</v>
       </c>
       <c r="V11" t="n">
         <v>-0.3282</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.629</v>
+        <v>-1.9533</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.256</v>
+        <v>-2.5803</v>
       </c>
       <c r="F12" t="n">
         <v>0.627</v>
@@ -1390,10 +1390,10 @@
         <v>1.1585</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1654</v>
+        <v>0.5103</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3036</v>
+        <v>0.3722</v>
       </c>
       <c r="U12" t="n">
         <v>0.1381</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>14.9128</v>
+        <v>15.46479999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>1.3381</v>
+        <v>1.8899</v>
       </c>
       <c r="F13" t="n">
         <v>13.5749</v>
@@ -1435,7 +1435,7 @@
         <v>11.9657</v>
       </c>
       <c r="H13" t="n">
-        <v>2.414299999999999</v>
+        <v>2.4143</v>
       </c>
       <c r="I13" t="n">
         <v>9.5512</v>
@@ -1459,7 +1459,7 @@
         <v>7.1316</v>
       </c>
       <c r="P13" t="n">
-        <v>1.930900000000001</v>
+        <v>1.9309</v>
       </c>
       <c r="Q13" t="n">
         <v>-10.6194</v>
@@ -1468,16 +1468,16 @@
         <v>12.5501</v>
       </c>
       <c r="S13" t="n">
-        <v>4.8275</v>
+        <v>5.3794</v>
       </c>
       <c r="T13" t="n">
-        <v>3.1683</v>
+        <v>3.7204</v>
       </c>
       <c r="U13" t="n">
-        <v>1.659</v>
+        <v>1.6591</v>
       </c>
       <c r="V13" t="n">
-        <v>-3.810999999999999</v>
+        <v>-3.811</v>
       </c>
       <c r="W13" t="n">
         <v>2.570400000000001</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.375299999999999</v>
+        <v>6.9163</v>
       </c>
       <c r="E14" t="n">
-        <v>5.7972</v>
+        <v>4.3493</v>
       </c>
       <c r="F14" t="n">
-        <v>2.5781</v>
+        <v>2.567</v>
       </c>
       <c r="G14" t="n">
         <v>2.9562</v>
@@ -1546,13 +1546,13 @@
         <v>1.3515</v>
       </c>
       <c r="S14" t="n">
-        <v>1.5004</v>
+        <v>0.0414</v>
       </c>
       <c r="T14" t="n">
-        <v>1.9577</v>
+        <v>0.5098</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4574</v>
+        <v>-0.4685</v>
       </c>
       <c r="V14" t="n">
         <v>3.7257</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. PIZARRO</t>
+          <t>J. FERMIN DE LUNA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,58 +1579,58 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6248</v>
+        <v>0.7677</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8697</v>
+        <v>0.3438</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.2448</v>
+        <v>0.4238</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.8545</v>
+        <v>0.2397</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2758</v>
+        <v>-1.7723</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.1303</v>
+        <v>2.0119</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.2607</v>
+        <v>0.289</v>
       </c>
       <c r="K15" t="n">
-        <v>0.3451</v>
+        <v>-1.0131</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.6058</v>
+        <v>1.3022</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.5939</v>
+        <v>-0.0494</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.0693</v>
+        <v>-0.7591</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.5245</v>
+        <v>0.7098</v>
       </c>
       <c r="P15" t="n">
-        <v>0.3862</v>
+        <v>0.9654</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.1931</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.5792</v>
+        <v>0.9654</v>
       </c>
       <c r="S15" t="n">
-        <v>1.3788</v>
+        <v>-0.1518</v>
       </c>
       <c r="T15" t="n">
-        <v>1.3234</v>
+        <v>0.0548</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0554</v>
+        <v>-0.2066</v>
       </c>
       <c r="V15" t="n">
         <v>-0.2856</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. FERMIN DE LUNA</t>
+          <t>J. MOLINA MELENDEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.456</v>
+        <v>-0.2962</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3438</v>
+        <v>-1.5708</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1121</v>
+        <v>1.2746</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2397</v>
+        <v>-0.906</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.7723</v>
+        <v>0.1452</v>
       </c>
       <c r="I16" t="n">
-        <v>2.0119</v>
+        <v>-1.0511</v>
       </c>
       <c r="J16" t="n">
-        <v>0.289</v>
+        <v>-0.6768</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.0131</v>
+        <v>0.2838</v>
       </c>
       <c r="L16" t="n">
-        <v>1.3022</v>
+        <v>-0.9606</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.0494</v>
+        <v>-0.2292</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.7591</v>
+        <v>-0.1387</v>
       </c>
       <c r="O16" t="n">
-        <v>0.7098</v>
+        <v>-0.0905</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9654</v>
+        <v>0.3862</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.3515</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9654</v>
+        <v>1.7377</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4635</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0548</v>
+        <v>-0.4419</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5183</v>
+        <v>-0.2339</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.2856</v>
+        <v>0.8995</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.8995</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2856</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. MOLINA MELENDEZ</t>
+          <t>M. PIZARRO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.9498</v>
+        <v>-0.5128</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.3982</v>
+        <v>-0.268</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4484</v>
+        <v>-0.2448</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.906</v>
+        <v>-0.8545</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1452</v>
+        <v>0.2758</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.0511</v>
+        <v>-1.1303</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.6768</v>
+        <v>-0.2607</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2838</v>
+        <v>0.3451</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.9606</v>
+        <v>-0.6058</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.2292</v>
+        <v>-0.5939</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1387</v>
+        <v>-0.0693</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.0905</v>
+        <v>-0.5245</v>
       </c>
       <c r="P17" t="n">
         <v>0.3862</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.3515</v>
+        <v>-0.1931</v>
       </c>
       <c r="R17" t="n">
-        <v>1.7377</v>
+        <v>0.5792</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.3294</v>
+        <v>0.2412</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.2693</v>
+        <v>0.1858</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0601</v>
+        <v>0.0554</v>
       </c>
       <c r="V17" t="n">
-        <v>0.8995</v>
+        <v>-0.2856</v>
       </c>
       <c r="W17" t="n">
-        <v>0.8995</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.2655</v>
+        <v>-0.9593</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.4831</v>
+        <v>-0.2763</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.7824</v>
+        <v>-0.6831</v>
       </c>
       <c r="G18" t="n">
         <v>-1.4285</v>
@@ -1858,13 +1858,13 @@
         <v>0.1931</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2924</v>
+        <v>0.0138</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.138</v>
+        <v>0.0688</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1544</v>
+        <v>-0.0551</v>
       </c>
       <c r="V18" t="n">
         <v>1.2277</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.3014</v>
+        <v>-1.2725</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.69</v>
+        <v>-1.5866</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3886</v>
+        <v>0.3141</v>
       </c>
       <c r="G19" t="n">
         <v>-0.8559</v>
@@ -1936,13 +1936,13 @@
         <v>0.5792</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5461</v>
+        <v>-0.5171</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2207</v>
+        <v>-0.1173</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3253</v>
+        <v>-0.3998</v>
       </c>
       <c r="V19" t="n">
         <v>-0.2856</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.3315</v>
+        <v>-1.9</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.5744</v>
+        <v>-2.0573</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2429</v>
+        <v>0.1573</v>
       </c>
       <c r="G20" t="n">
         <v>-0.9209000000000001</v>
@@ -2014,13 +2014,13 @@
         <v>1.9308</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.6383</v>
+        <v>-1.2068</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.4072</v>
+        <v>-0.8901</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2311</v>
+        <v>-0.3167</v>
       </c>
       <c r="V20" t="n">
         <v>0.6138</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.6858</v>
+        <v>-2.0693</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.918</v>
+        <v>-1.4009</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7678</v>
+        <v>-0.6685</v>
       </c>
       <c r="G21" t="n">
         <v>-2.4564</v>
@@ -2092,13 +2092,13 @@
         <v>0.9654</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6235000000000001</v>
+        <v>-0.0071</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6071</v>
+        <v>-0.09</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0164</v>
+        <v>0.083</v>
       </c>
       <c r="V21" t="n">
         <v>-0.5712</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.7212</v>
+        <v>-2.6111</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.4371</v>
+        <v>-1.7132</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.2841</v>
+        <v>-0.8979</v>
       </c>
       <c r="G22" t="n">
         <v>0.5266</v>
@@ -2170,13 +2170,13 @@
         <v>1.5446</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.5101</v>
+        <v>-1.4</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.352</v>
+        <v>-0.6281</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.1581</v>
+        <v>-0.7719</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.802</v>
+        <v>-5.7524</v>
       </c>
       <c r="E23" t="n">
         <v>-5.2069</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.5951</v>
+        <v>-0.5454</v>
       </c>
       <c r="G23" t="n">
         <v>-5.2423</v>
@@ -2248,13 +2248,13 @@
         <v>0.1931</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0497</v>
+        <v>-0.0001</v>
       </c>
       <c r="T23" t="n">
         <v>0.1377</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1874</v>
+        <v>-0.1377</v>
       </c>
       <c r="V23" t="n">
         <v>1.2277</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.3119</v>
+        <v>-6.5339</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.8778</v>
+        <v>-4.1881</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.434</v>
+        <v>-2.3458</v>
       </c>
       <c r="G24" t="n">
         <v>-3.0235</v>
@@ -2326,13 +2326,13 @@
         <v>0.5792</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2537</v>
+        <v>-0.4758</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1383</v>
+        <v>-0.4485</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1155</v>
+        <v>-0.0272</v>
       </c>
       <c r="V24" t="n">
         <v>-2.4554</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-14.913</v>
+        <v>-14.2235</v>
       </c>
       <c r="E25" t="n">
-        <v>-13.5748</v>
+        <v>-13.575</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.338100000000001</v>
+        <v>-0.6487000000000003</v>
       </c>
       <c r="G25" t="n">
         <v>-11.9655</v>
@@ -2380,7 +2380,7 @@
         <v>-5.747199999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>1.384400000000001</v>
+        <v>1.3844</v>
       </c>
       <c r="L25" t="n">
         <v>-7.1316</v>
@@ -2395,7 +2395,7 @@
         <v>-2.4195</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.930600000000001</v>
+        <v>-1.9306</v>
       </c>
       <c r="Q25" t="n">
         <v>-12.5501</v>
@@ -2404,13 +2404,13 @@
         <v>10.6192</v>
       </c>
       <c r="S25" t="n">
-        <v>-4.8275</v>
+        <v>-4.138199999999999</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.659000000000001</v>
+        <v>-1.659</v>
       </c>
       <c r="U25" t="n">
-        <v>-3.1686</v>
+        <v>-2.479</v>
       </c>
       <c r="V25" t="n">
         <v>3.810999999999999</v>
